--- a/naver-place-crawler/results_health/서면_PT.xlsx
+++ b/naver-place-crawler/results_health/서면_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="47" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 범일로 161-1 SJ파베르 건물 3층</t>
+          <t>부산 부산진구 범일로 161-1 SJ파베르 건물 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42t3n</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>O</t>
@@ -624,10 +628,10 @@
         <v>345</v>
       </c>
       <c r="Q2" t="n">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="R2" t="n">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -653,34 +657,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
+          <t>글래드휘트니스 서면점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fmpt__teddy@naver.com</t>
+          <t>gladfitness_seomyeon@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1343-6817</t>
+          <t>051-802-9900</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
+          <t>부산 부산진구 동천로 4 지오플레이스 6층 6002호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sksoe31e</t>
+          <t>https://blog.naver.com/gladfitness_seomyeon/223250547892</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,18 +699,22 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4eq2q</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1086</v>
+        <v>628</v>
       </c>
       <c r="Q3" t="n">
-        <v>815</v>
+        <v>482</v>
       </c>
       <c r="R3" t="n">
-        <v>1901</v>
+        <v>1110</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1138689357</t>
+          <t>1673829593</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138689357</t>
+          <t>https://m.place.naver.com/place/1673829593</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -845,34 +853,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>��포츠시설</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>멋짐 서면점</t>
+          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mutgym8689@naver.com</t>
+          <t>fmpt__teddy@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1314-8689</t>
+          <t>0507-1343-6817</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
+          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym8689</t>
+          <t>https://open.kakao.com/o/sksoe31e</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -887,18 +895,22 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4fpwi</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -907,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1411</v>
+        <v>1086</v>
       </c>
       <c r="Q5" t="n">
-        <v>1047</v>
+        <v>818</v>
       </c>
       <c r="R5" t="n">
-        <v>2458</v>
+        <v>1904</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1024587035</t>
+          <t>1138689357</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024587035</t>
+          <t>https://m.place.naver.com/place/1138689357</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -944,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>멋짐 서면2호점</t>
+          <t>멋짐 서면점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mutgym_@naver.com</t>
+          <t>mutgym8689@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1378-8691</t>
+          <t>0507-1314-8689</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 중앙대로666번길 50 201동 지하2층 5-13호</t>
+          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mutgym_seomyeon_2</t>
+          <t>https://blog.naver.com/mutgym8689</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -981,15 +993,19 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4h77f</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1001,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>517</v>
+        <v>1413</v>
       </c>
       <c r="Q6" t="n">
-        <v>400</v>
+        <v>1048</v>
       </c>
       <c r="R6" t="n">
-        <v>917</v>
+        <v>2461</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2036420985</t>
+          <t>1024587035</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2036420985</t>
+          <t>https://m.place.naver.com/place/1024587035</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1038,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>마카라멀티짐 서면점</t>
+          <t>멋짐 서면2호점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>jhs850720@naver.com</t>
+          <t>mutgym_@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1319-8423</t>
+          <t>0507-1378-8691</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 서면로 56 서면시장 3층</t>
+          <t>부산 부산진구 중앙대로666번길 50 201동 지하2층 5-13호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jhs850720</t>
+          <t>https://www.instagram.com/mutgym_seomyeon_2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1075,15 +1091,19 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wm5u9og</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1095,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>270</v>
+        <v>517</v>
       </c>
       <c r="Q7" t="n">
-        <v>886</v>
+        <v>400</v>
       </c>
       <c r="R7" t="n">
-        <v>1156</v>
+        <v>917</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>33964145</t>
+          <t>2036420985</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33964145</t>
+          <t>https://m.place.naver.com/place/2036420985</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1132,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>서면PT &amp; 헬스 놈짐 전포본점</t>
+          <t>마카라멀티짐 서면점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nomgym@naver.com</t>
+          <t>jhs850720@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1448-6113</t>
+          <t>0507-1319-8423</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 동천로 62 2F 서면PT &amp; 헬스 놈짐 전포본점</t>
+          <t>부산 부산진구 서면로 56 서면시장 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nom_gym</t>
+          <t>https://blog.naver.com/jhs850720</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1169,15 +1189,19 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4dqw0</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1189,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1360</v>
+        <v>270</v>
       </c>
       <c r="Q8" t="n">
-        <v>785</v>
+        <v>886</v>
       </c>
       <c r="R8" t="n">
-        <v>2145</v>
+        <v>1156</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1845202882</t>
+          <t>33964145</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845202882</t>
+          <t>https://m.place.naver.com/place/33964145</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1221,34 +1245,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>우노짐 헬스&amp;PT 서면점</t>
+          <t>서면PT &amp; 헬스 놈짐 전포본점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>unogym_1@naver.com</t>
+          <t>nomgym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1426-0888</t>
+          <t>0507-1448-6113</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 부전로 94 영동프라자 3층</t>
+          <t>부산 부산진구 동천로 62 2F 서면PT &amp; 헬스 놈짐 전포본점</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/unogym_1</t>
+          <t>https://www.instagram.com/nom_gym</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1263,15 +1287,19 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w423c4</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1283,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>70</v>
+        <v>1360</v>
       </c>
       <c r="Q9" t="n">
-        <v>28</v>
+        <v>785</v>
       </c>
       <c r="R9" t="n">
-        <v>98</v>
+        <v>2145</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026422991</t>
+          <t>1845202882</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2026422991</t>
+          <t>https://m.place.naver.com/place/1845202882</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1315,34 +1343,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>뉴짐스</t>
+          <t>코코아짐 헬스 PT 스쿼시 범내골역점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>newgyms@naver.com</t>
+          <t>cocoagymbn@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1313-2236</t>
+          <t>0507-1374-1945</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 서전로38번길 66 3층</t>
+          <t>부산 부산진구 범일로 181 지하1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/n.gyms_official</t>
+          <t>https://blog.naver.com/cocoagymbn</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1357,15 +1385,19 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/whhuq4g</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1377,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="Q10" t="n">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c r="R10" t="n">
-        <v>124</v>
+        <v>153</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,12 +1424,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1810951830</t>
+          <t>2057373274</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1810951830</t>
+          <t>https://m.place.naver.com/place/2057373274</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1409,34 +1441,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>태닝</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>홀리탠 태닝샵 부산서면점</t>
+          <t>아르케 핏 PT 서면전포점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>susennes8722@naver.com</t>
+          <t>zon_t@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1386-9045</t>
+          <t>0507-1345-6738</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산 부산진구 가야대로784번길 46-14 2층 202호</t>
+          <t>부산 부산진구 전포대로209번길 43 아세아빌딩 지하1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/susennes8722</t>
+          <t>https://www.instagram.com/arkhe_fit</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1451,7 +1483,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1461,7 +1493,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ei4i</t>
+          <t>https://talk.naver.com/ct/w42pxo</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1475,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1125</v>
+        <v>157</v>
       </c>
       <c r="Q11" t="n">
-        <v>41</v>
+        <v>316</v>
       </c>
       <c r="R11" t="n">
-        <v>1166</v>
+        <v>473</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1490,109 +1522,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1386417998</t>
+          <t>1578556277</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1386417998</t>
+          <t>https://m.place.naver.com/place/1578556277</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>라벨짐 전포점 헬스&amp;PT</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>labelgym2@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1473-2259</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>부산광역시 부산진구 동성로 136 4층 401호</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/labelgym2</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>223</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>316</v>
-      </c>
-      <c r="R12" t="n">
-        <v>539</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1949510224</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1949510224</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-14</t>
         </is>

--- a/naver-place-crawler/results_health/서면_PT.xlsx
+++ b/naver-place-crawler/results_health/서면_PT.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -657,34 +657,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
+          <t>글래드휘트니스 서면점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fmpt__teddy@naver.com</t>
+          <t>gladfitness_seomyeon@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1343-6817</t>
+          <t>051-802-9900</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
+          <t>부산 부산진구 동천로 4 지오플레이스 6층 6002호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sksoe31e</t>
+          <t>https://blog.naver.com/gladfitness_seomyeon/223250547892</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4fpwi</t>
+          <t>https://talk.naver.com/ct/w4eq2q</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1092</v>
+        <v>632</v>
       </c>
       <c r="Q3" t="n">
-        <v>845</v>
+        <v>489</v>
       </c>
       <c r="R3" t="n">
-        <v>1937</v>
+        <v>1121</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1138689357</t>
+          <t>1673829593</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138689357</t>
+          <t>https://m.place.naver.com/place/1673829593</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -755,34 +755,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>다이어트,비만</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>비엘 다이어트</t>
+          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>aza_kk@naver.com</t>
+          <t>fmpt__teddy@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1433-8228</t>
+          <t>0507-1343-6817</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산 부산진구 동성로 119 2층(전포동) 효성빌리지</t>
+          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://open.kakao.com/o/sUmye2ib</t>
+          <t>https://open.kakao.com/o/sksoe31e</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w48cis</t>
+          <t>https://talk.naver.com/ct/w4fpwi</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>234</v>
+        <v>1092</v>
       </c>
       <c r="Q4" t="n">
-        <v>197</v>
+        <v>847</v>
       </c>
       <c r="R4" t="n">
-        <v>431</v>
+        <v>1939</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1168689366</t>
+          <t>1138689357</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1168689366</t>
+          <t>https://m.place.naver.com/place/1138689357</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1531,6 +1531,202 @@
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>뉴짐스</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>newgyms@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1313-2236</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>부산 부산진구 서전로38번길 66 3층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/n.gyms_official</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w438s8</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>60</v>
+      </c>
+      <c r="R12" t="n">
+        <v>126</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1810951830</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1810951830</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>태닝</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>홀리탠 태닝샵 부산서면점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>susennes8722@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1386-9045</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>부산 부산진구 가야대로784번길 46-14 2층 202호</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/susennes8722/224253285551</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ei4i</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>1151</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>41</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1192</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1386417998</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1386417998</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/서면_PT.xlsx
+++ b/naver-place-crawler/results_health/서면_PT.xlsx
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="47" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산 부산진구 범일로 161-1 SJ파베르 건물 3층</t>
+          <t>부산광역시 부산진구 범일로 161-1 SJ파베르 건물 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42t3n</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>O</t>
@@ -679,7 +675,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 4 지오플레이스 6층 6002호</t>
+          <t>부산광역시 부산진구 동천로 4 지오플레이스 6층 6002호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4eq2q</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -777,7 +769,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
+          <t>부산광역시 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -802,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4fpwi</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>O</t>
@@ -821,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="Q4" t="n">
         <v>847</v>
       </c>
       <c r="R4" t="n">
-        <v>1939</v>
+        <v>1941</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -875,7 +863,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
+          <t>부산광역시 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -900,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4h77f</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -973,7 +957,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산 부산진구 서면로 56 서면시장 3층</t>
+          <t>부산광역시 부산진구 서면로 56 서면시장 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -998,14 +982,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4dqw0</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1071,7 +1051,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 부산진구 중앙대로666번길 50 201동 지하2층 5-13호</t>
+          <t>부산광역시 부산진구 중앙대로666번길 50 201동 지하2층 5-13호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1096,14 +1076,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wm5u9og</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1169,7 +1145,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 62 2F 서면PT &amp; 헬스 놈짐 전포본점</t>
+          <t>부산광역시 부산진구 동천로 62 2F 서면PT &amp; 헬스 놈짐 전포본점</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1194,14 +1170,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w423c4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1267,7 +1239,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 부산진구 전포대로209번길 43 아세아빌딩 지하1층</t>
+          <t>부산광역시 부산진구 전포대로209번길 43 아세아빌딩 지하1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1292,14 +1264,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42pxo</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1314,10 +1282,10 @@
         <v>157</v>
       </c>
       <c r="Q9" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="R9" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1365,7 +1333,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산 부산진구 부전로 94 영동프라자 3층</t>
+          <t>부산광역시 부산진구 부전로 94 영동프라자 3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1390,14 +1358,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w0m3yqq</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1463,7 +1427,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산 부산진구 전포대로 207 3층 모션업PT</t>
+          <t>부산광역시 부산진구 전포대로 207 3층 모션업PT</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1488,14 +1452,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wsi0guq</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1561,7 +1521,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>부산 부산진구 서전로38번길 66 3층</t>
+          <t>부산광역시 부산진구 서전로38번길 66 3층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1586,14 +1546,10 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w438s8</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1703,13 +1659,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="Q13" t="n">
         <v>41</v>
       </c>
       <c r="R13" t="n">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/서면_PT.xlsx
+++ b/naver-place-crawler/results_health/서면_PT.xlsx
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="47" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 범일로 161-1 SJ파베르 건물 3층</t>
+          <t>부산 부산진구 범일로 161-1 SJ파베르 건물 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42t3n</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>O</t>
@@ -675,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 동천로 4 지오플레이스 6층 6002호</t>
+          <t>부산 부산진구 동천로 4 지오플레이스 6층 6002호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4eq2q</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -769,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
+          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -794,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4fpwi</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>O</t>
@@ -809,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="Q4" t="n">
         <v>847</v>
       </c>
       <c r="R4" t="n">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -863,7 +875,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
+          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -888,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4h77f</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -957,7 +973,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 서면로 56 서면시장 3층</t>
+          <t>부산 부산진구 서면로 56 서면시장 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -982,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4dqw0</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1051,7 +1071,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 중앙대로666번길 50 201동 지하2층 5-13호</t>
+          <t>부산 부산진구 중앙대로666번길 50 201동 지하2층 5-13호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1076,10 +1096,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wm5u9og</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1094,10 +1118,10 @@
         <v>534</v>
       </c>
       <c r="Q7" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="R7" t="n">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1145,7 +1169,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 동천로 62 2F 서면PT &amp; 헬스 놈짐 전포본점</t>
+          <t>부산 부산진구 동천로 62 2F 서면PT &amp; 헬스 놈짐 전포본점</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1170,10 +1194,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w423c4</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1239,7 +1267,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 전포대로209번길 43 아세아빌딩 지하1층</t>
+          <t>부산 부산진구 전포대로209번길 43 아세아빌딩 지하1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1264,10 +1292,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42pxo</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1311,34 +1343,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>우노짐 헬스&amp;PT 서면점</t>
+          <t>모션업PT 전포 6호점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>unogym_1@naver.com</t>
+          <t>motionuppt2879@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1426-0888</t>
+          <t>0507-1487-7556</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 부전로 94 영동프라자 3층</t>
+          <t>부산 부산진구 전포대로 207 3층 모션업PT</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/unogym_1</t>
+          <t>https://blog.naver.com/motionuppt2879</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1358,10 +1390,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wsi0guq</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1373,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>84</v>
+        <v>231</v>
       </c>
       <c r="Q10" t="n">
-        <v>31</v>
+        <v>708</v>
       </c>
       <c r="R10" t="n">
-        <v>115</v>
+        <v>939</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1424,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026422991</t>
+          <t>1594058930</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2026422991</t>
+          <t>https://m.place.naver.com/place/1594058930</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1410,29 +1446,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>모션업PT 전포 6호점</t>
+          <t>뉴짐스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>motionuppt2879@naver.com</t>
+          <t>newgyms@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1487-7556</t>
+          <t>0507-1313-2236</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 전포대로 207 3층 모션업PT</t>
+          <t>부산 부산진구 서전로38번길 66 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/motionuppt2879</t>
+          <t>https://www.instagram.com/n.gyms_official</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1447,15 +1483,19 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w438s8</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1467,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>231</v>
+        <v>66</v>
       </c>
       <c r="Q11" t="n">
-        <v>708</v>
+        <v>60</v>
       </c>
       <c r="R11" t="n">
-        <v>939</v>
+        <v>126</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,12 +1522,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1594058930</t>
+          <t>1810951830</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1594058930</t>
+          <t>https://m.place.naver.com/place/1810951830</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1499,34 +1539,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>태닝</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>뉴짐스</t>
+          <t>홀리탠 태닝샵 부산서면점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>newgyms@naver.com</t>
+          <t>susennes8722@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1313-2236</t>
+          <t>0507-1386-9045</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 서전로38번길 66 3층</t>
+          <t>부산 부산진구 가야대로784번길 46-14 2층 202호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/n.gyms_official</t>
+          <t>https://blog.naver.com/susennes8722/224253285551</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1541,15 +1581,19 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ei4i</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1561,13 +1605,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>66</v>
+        <v>1152</v>
       </c>
       <c r="Q12" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="R12" t="n">
-        <v>126</v>
+        <v>1193</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,12 +1620,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1810951830</t>
+          <t>1386417998</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1810951830</t>
+          <t>https://m.place.naver.com/place/1386417998</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1593,34 +1637,34 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>태닝</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>홀리탠 태닝샵 부산서면점</t>
+          <t>라벨짐 전포점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>susennes8722@naver.com</t>
+          <t>labelgym2@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1386-9045</t>
+          <t>0507-1473-2259</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>부산 부산진구 가야대로784번길 46-14 2층 202호</t>
+          <t>부산 부산진구 동성로 136 4층 401호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/susennes8722/224253285551</t>
+          <t>https://blog.naver.com/labelgym2</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1645,7 +1689,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ei4i</t>
+          <t>https://talk.naver.com/ct/w4dago</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1659,13 +1703,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1152</v>
+        <v>223</v>
       </c>
       <c r="Q13" t="n">
-        <v>41</v>
+        <v>319</v>
       </c>
       <c r="R13" t="n">
-        <v>1193</v>
+        <v>542</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1674,12 +1718,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1386417998</t>
+          <t>1949510224</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1386417998</t>
+          <t>https://m.place.naver.com/place/1949510224</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">

--- a/naver-place-crawler/results_health/서면_PT.xlsx
+++ b/naver-place-crawler/results_health/서면_PT.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -650,41 +650,41 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>글래드휘트니스 서면점</t>
+          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>gladfitness_seomyeon@naver.com</t>
+          <t>fmpt__teddy@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>051-802-9900</t>
+          <t>0507-1343-6817</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 4 지오플레이스 6층 6002호</t>
+          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gladfitness_seomyeon/223250547892</t>
+          <t>https://open.kakao.com/o/sksoe31e</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4eq2q</t>
+          <t>https://talk.naver.com/ct/w4fpwi</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>632</v>
+        <v>1093</v>
       </c>
       <c r="Q3" t="n">
-        <v>489</v>
+        <v>847</v>
       </c>
       <c r="R3" t="n">
-        <v>1121</v>
+        <v>1940</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1673829593</t>
+          <t>1138689357</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1673829593</t>
+          <t>https://m.place.naver.com/place/1138689357</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
+          <t>멋짐 서면점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>fmpt__teddy@naver.com</t>
+          <t>mutgym8689@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1343-6817</t>
+          <t>0507-1314-8689</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
+          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sksoe31e</t>
+          <t>https://blog.naver.com/mutgym8689</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4fpwi</t>
+          <t>https://talk.naver.com/ct/w4h77f</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1093</v>
+        <v>1441</v>
       </c>
       <c r="Q4" t="n">
-        <v>847</v>
+        <v>1056</v>
       </c>
       <c r="R4" t="n">
-        <v>1940</v>
+        <v>2497</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1138689357</t>
+          <t>1024587035</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138689357</t>
+          <t>https://m.place.naver.com/place/1024587035</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -858,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>멋짐 서면점</t>
+          <t>마카라멀티짐 서면점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mutgym8689@naver.com</t>
+          <t>jhs850720@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1314-8689</t>
+          <t>0507-1319-8423</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
+          <t>부산 부산진구 서면로 56 서면시장 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym8689</t>
+          <t>https://blog.naver.com/jhs850720</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4h77f</t>
+          <t>https://talk.naver.com/ct/w4dqw0</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1441</v>
+        <v>272</v>
       </c>
       <c r="Q5" t="n">
-        <v>1056</v>
+        <v>901</v>
       </c>
       <c r="R5" t="n">
-        <v>2497</v>
+        <v>1173</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +934,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1024587035</t>
+          <t>33964145</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024587035</t>
+          <t>https://m.place.naver.com/place/33964145</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -956,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>마카라멀티짐 서면점</t>
+          <t>멋짐 서면2호점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>jhs850720@naver.com</t>
+          <t>mutgym_@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1319-8423</t>
+          <t>0507-1378-8691</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산 부산진구 서면로 56 서면시장 3층</t>
+          <t>부산 부산진구 중앙대로666번길 50 201동 지하2층 5-13호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jhs850720</t>
+          <t>https://www.instagram.com/mutgym_seomyeon_2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4dqw0</t>
+          <t>https://talk.naver.com/ct/wm5u9og</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>272</v>
+        <v>534</v>
       </c>
       <c r="Q6" t="n">
-        <v>901</v>
+        <v>416</v>
       </c>
       <c r="R6" t="n">
-        <v>1173</v>
+        <v>950</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>33964145</t>
+          <t>2036420985</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33964145</t>
+          <t>https://m.place.naver.com/place/2036420985</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1054,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>멋짐 서면2호점</t>
+          <t>서면PT &amp; 헬스 놈짐 전포본점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mutgym_@naver.com</t>
+          <t>nomgym@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1378-8691</t>
+          <t>0507-1448-6113</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 부산진구 중앙대로666번길 50 201동 지하2층 5-13호</t>
+          <t>부산 부산진구 동천로 62 2F 서면PT &amp; 헬스 놈짐 전포본점</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mutgym_seomyeon_2</t>
+          <t>https://www.instagram.com/nom_gym</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wm5u9og</t>
+          <t>https://talk.naver.com/ct/w423c4</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>534</v>
+        <v>1377</v>
       </c>
       <c r="Q7" t="n">
-        <v>416</v>
+        <v>820</v>
       </c>
       <c r="R7" t="n">
-        <v>950</v>
+        <v>2197</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1130,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2036420985</t>
+          <t>1845202882</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2036420985</t>
+          <t>https://m.place.naver.com/place/1845202882</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1152,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>서면PT &amp; 헬스 놈짐 전포본점</t>
+          <t>아르케 핏 PT 서면전포점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nomgym@naver.com</t>
+          <t>zon_t@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1448-6113</t>
+          <t>0507-1345-6738</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 62 2F 서면PT &amp; 헬스 놈짐 전포본점</t>
+          <t>부산 부산진구 전포대로209번길 43 아세아빌딩 지하1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nom_gym</t>
+          <t>https://www.instagram.com/arkhe_fit</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w423c4</t>
+          <t>https://talk.naver.com/ct/w42pxo</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1377</v>
+        <v>157</v>
       </c>
       <c r="Q8" t="n">
-        <v>820</v>
+        <v>321</v>
       </c>
       <c r="R8" t="n">
-        <v>2197</v>
+        <v>478</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1845202882</t>
+          <t>1578556277</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845202882</t>
+          <t>https://m.place.naver.com/place/1578556277</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>아르케 핏 PT 서면전포점</t>
+          <t>모션업PT 전포 6호점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>zon_t@naver.com</t>
+          <t>motionuppt2879@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1345-6738</t>
+          <t>0507-1487-7556</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 부산진구 전포대로209번길 43 아세아빌딩 지하1층</t>
+          <t>부산 부산진구 전포대로 207 3층 모션업PT</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/arkhe_fit</t>
+          <t>https://blog.naver.com/motionuppt2879</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w42pxo</t>
+          <t>https://talk.naver.com/ct/wsi0guq</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>157</v>
+        <v>231</v>
       </c>
       <c r="Q9" t="n">
-        <v>321</v>
+        <v>708</v>
       </c>
       <c r="R9" t="n">
-        <v>478</v>
+        <v>939</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,17 +1326,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1578556277</t>
+          <t>1594058930</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1578556277</t>
+          <t>https://m.place.naver.com/place/1594058930</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1348,29 +1348,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>모션업PT 전포 6호점</t>
+          <t>뉴짐스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>motionuppt2879@naver.com</t>
+          <t>newgyms@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1487-7556</t>
+          <t>0507-1313-2236</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산 부산진구 전포대로 207 3층 모션업PT</t>
+          <t>부산 부산진구 서전로38번길 66 3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/motionuppt2879</t>
+          <t>https://www.instagram.com/n.gyms_official</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wsi0guq</t>
+          <t>https://talk.naver.com/ct/w438s8</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1409,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>231</v>
+        <v>66</v>
       </c>
       <c r="Q10" t="n">
-        <v>708</v>
+        <v>60</v>
       </c>
       <c r="R10" t="n">
-        <v>939</v>
+        <v>126</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,51 +1424,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1594058930</t>
+          <t>1810951830</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1594058930</t>
+          <t>https://m.place.naver.com/place/1810951830</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>태닝</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>뉴짐스</t>
+          <t>홀리탠 태닝샵 부산서면점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>newgyms@naver.com</t>
+          <t>susennes8722@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1313-2236</t>
+          <t>0507-1386-9045</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산 부산진구 서전로38번길 66 3층</t>
+          <t>부산 부산진구 가야대로784번길 46-14 2층 202호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/n.gyms_official</t>
+          <t>https://blog.naver.com/susennes8722/224253285551</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w438s8</t>
+          <t>https://talk.naver.com/ct/w4ei4i</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>66</v>
+        <v>1152</v>
       </c>
       <c r="Q11" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="R11" t="n">
-        <v>126</v>
+        <v>1193</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,51 +1522,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1810951830</t>
+          <t>1386417998</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1810951830</t>
+          <t>https://m.place.naver.com/place/1386417998</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>태닝</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>홀리탠 태닝샵 부산서면점</t>
+          <t>라벨짐 전포점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>susennes8722@naver.com</t>
+          <t>labelgym2@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1386-9045</t>
+          <t>0507-1473-2259</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>부산 부산진구 가야대로784번길 46-14 2층 202호</t>
+          <t>부산 부산진구 동성로 136 4층 401호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/susennes8722/224253285551</t>
+          <t>https://blog.naver.com/labelgym2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ei4i</t>
+          <t>https://talk.naver.com/ct/w4dago</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1605,13 +1605,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1152</v>
+        <v>223</v>
       </c>
       <c r="Q12" t="n">
-        <v>41</v>
+        <v>319</v>
       </c>
       <c r="R12" t="n">
-        <v>1193</v>
+        <v>542</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1620,115 +1620,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1386417998</t>
+          <t>1949510224</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1386417998</t>
+          <t>https://m.place.naver.com/place/1949510224</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>라벨짐 전포점 헬스&amp;PT</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>labelgym2@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1473-2259</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>부산 부산진구 동성로 136 4층 401호</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/labelgym2</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4dago</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>223</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>319</v>
-      </c>
-      <c r="R13" t="n">
-        <v>542</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1949510224</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1949510224</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/서면_PT.xlsx
+++ b/naver-place-crawler/results_health/서면_PT.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="47" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산 부산진구 범일로 161-1 SJ파베르 건물 3층</t>
+          <t>부산광역시 부산진구 범일로 161-1 SJ파베르 건물 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42t3n</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>O</t>
@@ -657,34 +653,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
+          <t>글래드휘트니스 서면점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fmpt__teddy@naver.com</t>
+          <t>gladfitness_seomyeon@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1343-6817</t>
+          <t>051-802-9900</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
+          <t>부산광역시 부산진구 동천로 4 지오플레이스 6층 6002호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sksoe31e</t>
+          <t>https://blog.naver.com/gladfitness_seomyeon/223250547892</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,22 +695,18 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4fpwi</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1093</v>
+        <v>632</v>
       </c>
       <c r="Q3" t="n">
-        <v>847</v>
+        <v>489</v>
       </c>
       <c r="R3" t="n">
-        <v>1940</v>
+        <v>1121</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1138689357</t>
+          <t>1673829593</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138689357</t>
+          <t>https://m.place.naver.com/place/1673829593</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -760,34 +752,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>멋짐 서면점</t>
+          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mutgym8689@naver.com</t>
+          <t>fmpt__teddy@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1314-8689</t>
+          <t>0507-1343-6817</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
+          <t>부산광역시 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym8689</t>
+          <t>https://open.kakao.com/o/sksoe31e</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -797,22 +789,18 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4h77f</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -821,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1441</v>
+        <v>1093</v>
       </c>
       <c r="Q4" t="n">
-        <v>1056</v>
+        <v>847</v>
       </c>
       <c r="R4" t="n">
-        <v>2497</v>
+        <v>1940</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1024587035</t>
+          <t>1138689357</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024587035</t>
+          <t>https://m.place.naver.com/place/1138689357</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>마카라멀티짐 서면점</t>
+          <t>멋짐 서면점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>jhs850720@naver.com</t>
+          <t>mutgym8689@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1319-8423</t>
+          <t>0507-1314-8689</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산 부산진구 서면로 56 서면시장 3층</t>
+          <t>부산광역시 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jhs850720</t>
+          <t>https://blog.naver.com/mutgym8689</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -900,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4dqw0</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -919,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>272</v>
+        <v>1441</v>
       </c>
       <c r="Q5" t="n">
-        <v>901</v>
+        <v>1055</v>
       </c>
       <c r="R5" t="n">
-        <v>1173</v>
+        <v>2496</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>33964145</t>
+          <t>1024587035</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33964145</t>
+          <t>https://m.place.naver.com/place/1024587035</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -956,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>멋짐 서면2호점</t>
+          <t>마카라멀티짐 서면점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mutgym_@naver.com</t>
+          <t>jhs850720@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1378-8691</t>
+          <t>0507-1319-8423</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산 부산진구 중앙대로666번길 50 201동 지하2층 5-13호</t>
+          <t>부산광역시 부산진구 서면로 56 서면시장 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mutgym_seomyeon_2</t>
+          <t>https://blog.naver.com/jhs850720</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,19 +977,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wm5u9og</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1017,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>534</v>
+        <v>272</v>
       </c>
       <c r="Q6" t="n">
-        <v>416</v>
+        <v>901</v>
       </c>
       <c r="R6" t="n">
-        <v>950</v>
+        <v>1173</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2036420985</t>
+          <t>33964145</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2036420985</t>
+          <t>https://m.place.naver.com/place/33964145</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1054,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>서면PT &amp; 헬스 놈짐 전포본점</t>
+          <t>멋짐 서면2호점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nomgym@naver.com</t>
+          <t>mutgym_@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1448-6113</t>
+          <t>0507-1378-8691</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 62 2F 서면PT &amp; 헬스 놈짐 전포본점</t>
+          <t>부산광역시 부산진구 중앙대로666번길 50 201동 지하2층 5-13호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nom_gym</t>
+          <t>https://www.instagram.com/mutgym_seomyeon_2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1096,14 +1076,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w423c4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1115,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1377</v>
+        <v>534</v>
       </c>
       <c r="Q7" t="n">
-        <v>820</v>
+        <v>416</v>
       </c>
       <c r="R7" t="n">
-        <v>2197</v>
+        <v>950</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1845202882</t>
+          <t>2036420985</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845202882</t>
+          <t>https://m.place.naver.com/place/2036420985</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1152,29 +1128,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>아르케 핏 PT 서면전포점</t>
+          <t>서면PT &amp; 헬스 놈짐 전포본점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>zon_t@naver.com</t>
+          <t>nomgym@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1345-6738</t>
+          <t>0507-1448-6113</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산 부산진구 전포대로209번길 43 아세아빌딩 지하1층</t>
+          <t>부산광역시 부산진구 동천로 62 2F 서면PT &amp; 헬스 놈짐 전포본점</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/arkhe_fit</t>
+          <t>https://www.instagram.com/nom_gym</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1194,14 +1170,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42pxo</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1213,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>157</v>
+        <v>1377</v>
       </c>
       <c r="Q8" t="n">
-        <v>321</v>
+        <v>820</v>
       </c>
       <c r="R8" t="n">
-        <v>478</v>
+        <v>2197</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1200,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1578556277</t>
+          <t>1845202882</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1578556277</t>
+          <t>https://m.place.naver.com/place/1845202882</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1250,29 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>모션업PT 전포 6호점</t>
+          <t>아르케 핏 PT 서면전포점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>motionuppt2879@naver.com</t>
+          <t>geunieter@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1487-7556</t>
+          <t>0507-1345-6738</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 부산진구 전포대로 207 3층 모션업PT</t>
+          <t>부산 부산진구 전포대로209번길 43 아세아빌딩 지하1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/motionuppt2879</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1282,12 +1254,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1297,7 +1269,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wsi0guq</t>
+          <t>https://talk.naver.com/ct/w42pxo</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>231</v>
+        <v>157</v>
       </c>
       <c r="Q9" t="n">
-        <v>708</v>
+        <v>321</v>
       </c>
       <c r="R9" t="n">
-        <v>939</v>
+        <v>478</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1298,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1594058930</t>
+          <t>1578556277</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1594058930</t>
+          <t>https://m.place.naver.com/place/1578556277</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1348,29 +1320,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>뉴짐스</t>
+          <t>모션업PT 전포 6호점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>newgyms@naver.com</t>
+          <t>motionuppt2879@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1313-2236</t>
+          <t>0507-1487-7556</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산 부산진구 서전로38번길 66 3층</t>
+          <t>부산 부산진구 전포대로 207 3층 모션업PT</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/n.gyms_official</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1380,7 +1352,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1395,7 +1367,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w438s8</t>
+          <t>https://talk.naver.com/ct/wsi0guq</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1409,13 +1381,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>66</v>
+        <v>231</v>
       </c>
       <c r="Q10" t="n">
-        <v>60</v>
+        <v>708</v>
       </c>
       <c r="R10" t="n">
-        <v>126</v>
+        <v>939</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,12 +1396,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1810951830</t>
+          <t>1594058930</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1810951830</t>
+          <t>https://m.place.naver.com/place/1594058930</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1441,34 +1413,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>태닝</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>홀리탠 태닝샵 부산서면점</t>
+          <t>뉴짐스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>susennes8722@naver.com</t>
+          <t>newgyms@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1386-9045</t>
+          <t>0507-1313-2236</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산 부산진구 가야대로784번길 46-14 2층 202호</t>
+          <t>부산 부산진구 서전로38번길 66 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/susennes8722/224253285551</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1478,12 +1450,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1493,7 +1465,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ei4i</t>
+          <t>https://talk.naver.com/ct/w438s8</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1507,13 +1479,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1152</v>
+        <v>66</v>
       </c>
       <c r="Q11" t="n">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="R11" t="n">
-        <v>1193</v>
+        <v>126</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,113 +1494,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1386417998</t>
+          <t>1810951830</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1386417998</t>
+          <t>https://m.place.naver.com/place/1810951830</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>라벨짐 전포점 헬스&amp;PT</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>labelgym2@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1473-2259</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>부산 부산진구 동성로 136 4층 401호</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/labelgym2</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4dago</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>223</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>319</v>
-      </c>
-      <c r="R12" t="n">
-        <v>542</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1949510224</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1949510224</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/서면_PT.xlsx
+++ b/naver-place-crawler/results_health/서면_PT.xlsx
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="47" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 범일로 161-1 SJ파베르 건물 3층</t>
+          <t>부산 부산진구 범일로 161-1 SJ파베르 건물 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42t3n</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>O</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q2" t="n">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="R2" t="n">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -675,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 동천로 4 지오플레이스 6층 6002호</t>
+          <t>부산 부산진구 동천로 4 지오플레이스 6층 6002호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4eq2q</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -718,10 +726,10 @@
         <v>632</v>
       </c>
       <c r="Q3" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="R3" t="n">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -747,39 +755,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>다이어트,비만</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
+          <t>비엘 다이어트</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>fmpt__teddy@naver.com</t>
+          <t>aza_kk@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1343-6817</t>
+          <t>0507-1433-8228</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
+          <t>부산 부산진구 동성로 119 2층(전포동) 효성빌리지</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sksoe31e</t>
+          <t>http://open.kakao.com/o/sUmye2ib</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -794,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w48cis</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>O</t>
@@ -809,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1093</v>
+        <v>234</v>
       </c>
       <c r="Q4" t="n">
-        <v>847</v>
+        <v>197</v>
       </c>
       <c r="R4" t="n">
-        <v>1940</v>
+        <v>431</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1138689357</t>
+          <t>1168689366</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138689357</t>
+          <t>https://m.place.naver.com/place/1168689366</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>멋짐 서면점</t>
+          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mutgym8689@naver.com</t>
+          <t>fmpt__teddy@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1314-8689</t>
+          <t>0507-1343-6817</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
+          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym8689</t>
+          <t>https://open.kakao.com/o/sksoe31e</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -883,18 +895,22 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4fpwi</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -903,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1441</v>
+        <v>1093</v>
       </c>
       <c r="Q5" t="n">
-        <v>1055</v>
+        <v>847</v>
       </c>
       <c r="R5" t="n">
-        <v>2496</v>
+        <v>1940</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1024587035</t>
+          <t>1138689357</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024587035</t>
+          <t>https://m.place.naver.com/place/1138689357</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>마카라멀티짐 서면점</t>
+          <t>멋짐 서면점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>jhs850720@naver.com</t>
+          <t>mutgym8689@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1319-8423</t>
+          <t>0507-1314-8689</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 서면로 56 서면시장 3층</t>
+          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jhs850720</t>
+          <t>https://blog.naver.com/mutgym8689</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -982,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4h77f</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -997,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>272</v>
+        <v>1444</v>
       </c>
       <c r="Q6" t="n">
-        <v>901</v>
+        <v>1056</v>
       </c>
       <c r="R6" t="n">
-        <v>1173</v>
+        <v>2500</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>33964145</t>
+          <t>1024587035</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33964145</t>
+          <t>https://m.place.naver.com/place/1024587035</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1034,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>멋짐 서면2호점</t>
+          <t>마카라멀티짐 서면점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mutgym_@naver.com</t>
+          <t>jhs850720@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1378-8691</t>
+          <t>0507-1319-8423</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 중앙대로666번길 50 201동 지하2층 5-13호</t>
+          <t>부산 부산진구 서면로 56 서면시장 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mutgym_seomyeon_2</t>
+          <t>https://blog.naver.com/jhs850720</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1071,15 +1091,19 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4dqw0</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1091,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>534</v>
+        <v>273</v>
       </c>
       <c r="Q7" t="n">
-        <v>416</v>
+        <v>901</v>
       </c>
       <c r="R7" t="n">
-        <v>950</v>
+        <v>1174</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2036420985</t>
+          <t>33964145</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2036420985</t>
+          <t>https://m.place.naver.com/place/33964145</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1128,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>서면PT &amp; 헬스 놈짐 전포본점</t>
+          <t>멋짐 서면2호점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nomgym@naver.com</t>
+          <t>mutgym_@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1448-6113</t>
+          <t>0507-1378-8691</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 동천로 62 2F 서면PT &amp; 헬스 놈짐 전포본점</t>
+          <t>부산 부산진구 중앙대로666번길 50 201동 지하2층 5-13호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nom_gym</t>
+          <t>https://www.instagram.com/mutgym_seomyeon_2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1170,10 +1194,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wm5u9og</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1185,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1377</v>
+        <v>537</v>
       </c>
       <c r="Q8" t="n">
-        <v>820</v>
+        <v>418</v>
       </c>
       <c r="R8" t="n">
-        <v>2197</v>
+        <v>955</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1845202882</t>
+          <t>2036420985</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845202882</t>
+          <t>https://m.place.naver.com/place/2036420985</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1222,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>아르케 핏 PT 서면전포점</t>
+          <t>서면PT &amp; 헬스 놈짐 전포본점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>geunieter@naver.com</t>
+          <t>nomgym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1345-6738</t>
+          <t>0507-1448-6113</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 부산진구 전포대로209번길 43 아세아빌딩 지하1층</t>
+          <t>부산 부산진구 동천로 62 2F 서면PT &amp; 헬스 놈짐 전포본점</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nom_gym</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1254,7 +1282,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1269,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w42pxo</t>
+          <t>https://talk.naver.com/ct/w423c4</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1283,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>157</v>
+        <v>1377</v>
       </c>
       <c r="Q9" t="n">
-        <v>321</v>
+        <v>820</v>
       </c>
       <c r="R9" t="n">
-        <v>478</v>
+        <v>2197</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1578556277</t>
+          <t>1845202882</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1578556277</t>
+          <t>https://m.place.naver.com/place/1845202882</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1315,34 +1343,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>모션업PT 전포 6호점</t>
+          <t>코코아짐 헬스 PT 스쿼시 범내골역점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>motionuppt2879@naver.com</t>
+          <t>cocoagymbn@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1487-7556</t>
+          <t>0507-1374-1945</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산 부산진구 전포대로 207 3층 모션업PT</t>
+          <t>부산 부산진구 범일로 181 지하1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/cocoagymbn</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1352,12 +1380,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1367,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wsi0guq</t>
+          <t>https://talk.naver.com/ct/whhuq4g</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1381,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>231</v>
+        <v>53</v>
       </c>
       <c r="Q10" t="n">
-        <v>708</v>
+        <v>103</v>
       </c>
       <c r="R10" t="n">
-        <v>939</v>
+        <v>156</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1396,12 +1424,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1594058930</t>
+          <t>2057373274</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1594058930</t>
+          <t>https://m.place.naver.com/place/2057373274</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1418,29 +1446,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>뉴짐스</t>
+          <t>아르케 핏 PT 서면전포점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>newgyms@naver.com</t>
+          <t>zon_t@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1313-2236</t>
+          <t>0507-1345-6738</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산 부산진구 서전로38번길 66 3층</t>
+          <t>부산 부산진구 전포대로209번길 43 아세아빌딩 지하1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/arkhe_fit</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1450,7 +1478,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1465,7 +1493,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w438s8</t>
+          <t>https://talk.naver.com/ct/w42pxo</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1479,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>66</v>
+        <v>157</v>
       </c>
       <c r="Q11" t="n">
-        <v>60</v>
+        <v>322</v>
       </c>
       <c r="R11" t="n">
-        <v>126</v>
+        <v>479</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1494,12 +1522,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1810951830</t>
+          <t>1578556277</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1810951830</t>
+          <t>https://m.place.naver.com/place/1578556277</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/서면_PT.xlsx
+++ b/naver-place-crawler/results_health/서면_PT.xlsx
@@ -422,17 +422,17 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="47" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산 부산진구 범일로 161-1 SJ파베르 건물 3층</t>
+          <t>부산광역시 부산진구 범일로 161-1 SJ파베르 건물 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42t3n</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>O</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q2" t="n">
         <v>642</v>
       </c>
       <c r="R2" t="n">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,41 +646,41 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>글래드휘트니스 서면점</t>
+          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>gladfitness_seomyeon@naver.com</t>
+          <t>fmpt__teddy@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>051-802-9900</t>
+          <t>0507-1343-6817</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 4 지오플레이스 6층 6002호</t>
+          <t>부산광역시 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gladfitness_seomyeon/223250547892</t>
+          <t>https://open.kakao.com/o/sksoe31e</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,22 +695,18 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4eq2q</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>632</v>
+        <v>1092</v>
       </c>
       <c r="Q3" t="n">
-        <v>490</v>
+        <v>848</v>
       </c>
       <c r="R3" t="n">
-        <v>1122</v>
+        <v>1940</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1673829593</t>
+          <t>1138689357</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1673829593</t>
+          <t>https://m.place.naver.com/place/1138689357</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -846,7 +838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -858,29 +850,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
+          <t>멋짐 서면점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>fmpt__teddy@naver.com</t>
+          <t>mutgym8689@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1343-6817</t>
+          <t>0507-1314-8689</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
+          <t>부산광역시 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sksoe31e</t>
+          <t>https://blog.naver.com/mutgym8689</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -895,22 +887,18 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4fpwi</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -919,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1093</v>
+        <v>1445</v>
       </c>
       <c r="Q5" t="n">
-        <v>847</v>
+        <v>1056</v>
       </c>
       <c r="R5" t="n">
-        <v>1940</v>
+        <v>2501</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +922,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1138689357</t>
+          <t>1024587035</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138689357</t>
+          <t>https://m.place.naver.com/place/1024587035</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -956,29 +944,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>멋짐 서면점</t>
+          <t>마카라멀티짐 서면점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mutgym8689@naver.com</t>
+          <t>jhs850720@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1314-8689</t>
+          <t>0507-1319-8423</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
+          <t>부산광역시 부산진구 서면로 56 서면시장 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym8689</t>
+          <t>https://blog.naver.com/jhs850720</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -998,14 +986,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4h77f</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1017,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1444</v>
+        <v>273</v>
       </c>
       <c r="Q6" t="n">
-        <v>1056</v>
+        <v>901</v>
       </c>
       <c r="R6" t="n">
-        <v>2500</v>
+        <v>1174</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1016,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1024587035</t>
+          <t>33964145</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024587035</t>
+          <t>https://m.place.naver.com/place/33964145</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1054,29 +1038,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>마카라멀티짐 서면점</t>
+          <t>멋짐 서면2호점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>jhs850720@naver.com</t>
+          <t>mutgym_@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1319-8423</t>
+          <t>0507-1378-8691</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 부산진구 서면로 56 서면시장 3층</t>
+          <t>부산광역시 부산진구 중앙대로666번길 50 201동 지하2층 5-13호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jhs850720</t>
+          <t>https://www.instagram.com/mutgym_seomyeon_2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,19 +1075,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4dqw0</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1115,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>273</v>
+        <v>542</v>
       </c>
       <c r="Q7" t="n">
-        <v>901</v>
+        <v>418</v>
       </c>
       <c r="R7" t="n">
-        <v>1174</v>
+        <v>960</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1110,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>33964145</t>
+          <t>2036420985</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33964145</t>
+          <t>https://m.place.naver.com/place/2036420985</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1152,29 +1132,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>멋짐 서면2호점</t>
+          <t>서면PT &amp; 헬스 놈짐 전포본점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mutgym_@naver.com</t>
+          <t>nomgym@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1378-8691</t>
+          <t>0507-1448-6113</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산 부산진구 중앙대로666번길 50 201동 지하2층 5-13호</t>
+          <t>부산광역시 부산진구 동천로 62 2F 서면PT &amp; 헬스 놈짐 전포본점</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mutgym_seomyeon_2</t>
+          <t>https://www.instagram.com/nom_gym</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1194,14 +1174,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wm5u9og</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1213,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>537</v>
+        <v>1377</v>
       </c>
       <c r="Q8" t="n">
-        <v>418</v>
+        <v>820</v>
       </c>
       <c r="R8" t="n">
-        <v>955</v>
+        <v>2197</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1204,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2036420985</t>
+          <t>1845202882</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2036420985</t>
+          <t>https://m.place.naver.com/place/1845202882</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1226,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>서면PT &amp; 헬스 놈짐 전포본점</t>
+          <t>헬짐 HELL GYM</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nomgym@naver.com</t>
+          <t>hellgymseomyeon@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1448-6113</t>
+          <t>0507-1435-7378</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 62 2F 서면PT &amp; 헬스 놈짐 전포본점</t>
+          <t>부산광역시 부산진구 전포대로199번길 15 현대오피스텔 지하1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nom_gym</t>
+          <t>https://blog.naver.com/hellgymseomyeon</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1287,19 +1263,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w423c4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1311,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1377</v>
+        <v>729</v>
       </c>
       <c r="Q9" t="n">
-        <v>820</v>
+        <v>492</v>
       </c>
       <c r="R9" t="n">
-        <v>2197</v>
+        <v>1221</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,17 +1298,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1845202882</t>
+          <t>1847755059</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845202882</t>
+          <t>https://m.place.naver.com/place/1847755059</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1337,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산 부산진구 범일로 181 지하1층</t>
+          <t>부산광역시 부산진구 범일로 181 지하1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1390,14 +1362,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/whhuq4g</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1434,7 +1402,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1431,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산 부산진구 전포대로209번길 43 아세아빌딩 지하1층</t>
+          <t>부산광역시 부산진구 전포대로209번길 43 아세아빌딩 지하1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1488,14 +1456,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42pxo</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1532,7 +1496,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/서면_PT.xlsx
+++ b/naver-place-crawler/results_health/서면_PT.xlsx
@@ -422,17 +422,17 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="47" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 범일로 161-1 SJ파베르 건물 3층</t>
+          <t>부산 부산진구 범일로 161-1 SJ파베르 건물 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42t3n</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>O</t>
@@ -624,10 +628,10 @@
         <v>355</v>
       </c>
       <c r="Q2" t="n">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="R2" t="n">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -653,34 +657,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
+          <t>글래드휘트니스 서면점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fmpt__teddy@naver.com</t>
+          <t>gladfitness_seomyeon@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1343-6817</t>
+          <t>051-802-9900</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
+          <t>부산 부산진구 동천로 4 지오플레이스 6층 6002호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sksoe31e</t>
+          <t>https://blog.naver.com/gladfitness_seomyeon/223250547892</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,18 +699,22 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4eq2q</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1092</v>
+        <v>632</v>
       </c>
       <c r="Q3" t="n">
-        <v>848</v>
+        <v>490</v>
       </c>
       <c r="R3" t="n">
-        <v>1940</v>
+        <v>1122</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1138689357</t>
+          <t>1673829593</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138689357</t>
+          <t>https://m.place.naver.com/place/1673829593</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -747,34 +755,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>다이어트,비만</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>비엘 다이어트</t>
+          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>aza_kk@naver.com</t>
+          <t>fmpt__teddy@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1433-8228</t>
+          <t>0507-1343-6817</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산 부산진구 동성로 119 2층(전포동) 효성빌리지</t>
+          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://open.kakao.com/o/sUmye2ib</t>
+          <t>https://open.kakao.com/o/sksoe31e</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -799,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w48cis</t>
+          <t>https://talk.naver.com/ct/w4fpwi</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -813,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>234</v>
+        <v>1092</v>
       </c>
       <c r="Q4" t="n">
-        <v>197</v>
+        <v>849</v>
       </c>
       <c r="R4" t="n">
-        <v>431</v>
+        <v>1941</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1168689366</t>
+          <t>1138689357</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1168689366</t>
+          <t>https://m.place.naver.com/place/1138689357</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -867,7 +875,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
+          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -892,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4h77f</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -907,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="Q5" t="n">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="R5" t="n">
-        <v>2501</v>
+        <v>2503</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -961,7 +973,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 서면로 56 서면시장 3층</t>
+          <t>부산 부산진구 서면로 56 서면시장 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -986,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4dqw0</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1001,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q6" t="n">
         <v>901</v>
       </c>
       <c r="R6" t="n">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1055,7 +1071,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 중앙대로666번길 50 201동 지하2층 5-13호</t>
+          <t>부산 부산진구 중앙대로666번길 50 201동 지하2층 5-13호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1080,10 +1096,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wm5u9og</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1095,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="Q7" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="R7" t="n">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1149,7 +1169,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 동천로 62 2F 서면PT &amp; 헬스 놈짐 전포본점</t>
+          <t>부산 부산진구 동천로 62 2F 서면PT &amp; 헬스 놈짐 전포본점</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1174,10 +1194,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w423c4</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1189,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="Q8" t="n">
         <v>820</v>
       </c>
       <c r="R8" t="n">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1226,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>헬짐 HELL GYM</t>
+          <t>아르케 핏 PT 서면전포점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>hellgymseomyeon@naver.com</t>
+          <t>zon_t@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1435-7378</t>
+          <t>0507-1345-6738</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 전포대로199번길 15 현대오피스텔 지하1층</t>
+          <t>부산 부산진구 전포대로209번길 43 아세아빌딩 지하1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hellgymseomyeon</t>
+          <t>https://www.instagram.com/arkhe_fit</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1263,15 +1287,19 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42pxo</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1283,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>729</v>
+        <v>157</v>
       </c>
       <c r="Q9" t="n">
-        <v>492</v>
+        <v>323</v>
       </c>
       <c r="R9" t="n">
-        <v>1221</v>
+        <v>480</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1847755059</t>
+          <t>1578556277</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1847755059</t>
+          <t>https://m.place.naver.com/place/1578556277</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1320,29 +1348,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>코코아짐 헬스 PT 스쿼시 범내골역점</t>
+          <t>우노짐 헬스&amp;PT 서면점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cocoagymbn@naver.com</t>
+          <t>unogym_1@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1374-1945</t>
+          <t>0507-1426-0888</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 범일로 181 지하1층</t>
+          <t>부산 부산진구 부전로 94 영동프라자 3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cocoagymbn</t>
+          <t>https://blog.naver.com/unogym_1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1362,10 +1390,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w0m3yqq</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1377,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="Q10" t="n">
-        <v>103</v>
+        <v>31</v>
       </c>
       <c r="R10" t="n">
-        <v>156</v>
+        <v>115</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,12 +1424,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2057373274</t>
+          <t>2026422991</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2057373274</t>
+          <t>https://m.place.naver.com/place/2026422991</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1414,29 +1446,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>아르케 핏 PT 서면전포점</t>
+          <t>뉴짐스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>zon_t@naver.com</t>
+          <t>newgyms@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1345-6738</t>
+          <t>0507-1313-2236</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 전포대로209번길 43 아세아빌딩 지하1층</t>
+          <t>부산 부산진구 서전로38번길 66 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/arkhe_fit</t>
+          <t>https://www.instagram.com/n.gyms_official</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1456,10 +1488,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w438s8</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1471,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>157</v>
+        <v>66</v>
       </c>
       <c r="Q11" t="n">
-        <v>322</v>
+        <v>60</v>
       </c>
       <c r="R11" t="n">
-        <v>479</v>
+        <v>126</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,12 +1522,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1578556277</t>
+          <t>1810951830</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1578556277</t>
+          <t>https://m.place.naver.com/place/1810951830</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/서면_PT.xlsx
+++ b/naver-place-crawler/results_health/서면_PT.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q2" t="n">
         <v>643</v>
       </c>
       <c r="R2" t="n">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,41 +650,41 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>글래드휘트니스 서면점</t>
+          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>gladfitness_seomyeon@naver.com</t>
+          <t>fmpt__teddy@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>051-802-9900</t>
+          <t>0507-1343-6817</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 4 지오플레이스 6층 6002호</t>
+          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gladfitness_seomyeon/223250547892</t>
+          <t>https://open.kakao.com/o/sksoe31e</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4eq2q</t>
+          <t>https://talk.naver.com/ct/w4fpwi</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>632</v>
+        <v>1092</v>
       </c>
       <c r="Q3" t="n">
-        <v>490</v>
+        <v>849</v>
       </c>
       <c r="R3" t="n">
-        <v>1122</v>
+        <v>1941</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1673829593</t>
+          <t>1138689357</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1673829593</t>
+          <t>https://m.place.naver.com/place/1138689357</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
+          <t>마카라멀티짐 서면점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>fmpt__teddy@naver.com</t>
+          <t>jhs850720@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1343-6817</t>
+          <t>0507-1319-8423</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
+          <t>부산 부산진구 서면로 56 서면시장 3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sksoe31e</t>
+          <t>https://blog.naver.com/jhs850720</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4fpwi</t>
+          <t>https://talk.naver.com/ct/w4dqw0</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1092</v>
+        <v>275</v>
       </c>
       <c r="Q4" t="n">
-        <v>849</v>
+        <v>901</v>
       </c>
       <c r="R4" t="n">
-        <v>1941</v>
+        <v>1176</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1138689357</t>
+          <t>33964145</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138689357</t>
+          <t>https://m.place.naver.com/place/33964145</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -858,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>멋짐 서면점</t>
+          <t>멋짐 서면2호점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mutgym8689@naver.com</t>
+          <t>mutgym_@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1314-8689</t>
+          <t>0507-1378-8691</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
+          <t>부산 부산진구 중앙대로666번길 50 201동 지하2층 5-13호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym8689</t>
+          <t>https://www.instagram.com/mutgym_seomyeon_2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4h77f</t>
+          <t>https://talk.naver.com/ct/wm5u9og</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1446</v>
+        <v>544</v>
       </c>
       <c r="Q5" t="n">
-        <v>1057</v>
+        <v>419</v>
       </c>
       <c r="R5" t="n">
-        <v>2503</v>
+        <v>963</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +934,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1024587035</t>
+          <t>2036420985</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024587035</t>
+          <t>https://m.place.naver.com/place/2036420985</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -956,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>마카라멀티짐 서면점</t>
+          <t>서면PT &amp; 헬스 놈짐 전포본점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>jhs850720@naver.com</t>
+          <t>nomgym@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1319-8423</t>
+          <t>0507-1448-6113</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산 부산진구 서면로 56 서면시장 3층</t>
+          <t>부산 부산진구 동천로 62 2F 서면PT &amp; 헬스 놈짐 전포본점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jhs850720</t>
+          <t>https://www.instagram.com/nom_gym</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4dqw0</t>
+          <t>https://talk.naver.com/ct/w423c4</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>274</v>
+        <v>1378</v>
       </c>
       <c r="Q6" t="n">
-        <v>901</v>
+        <v>820</v>
       </c>
       <c r="R6" t="n">
-        <v>1175</v>
+        <v>2198</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>33964145</t>
+          <t>1845202882</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33964145</t>
+          <t>https://m.place.naver.com/place/1845202882</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1054,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>멋짐 서면2호점</t>
+          <t>오타쿠짐 서면점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mutgym_@naver.com</t>
+          <t>taehu12@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1378-8691</t>
+          <t>0507-1417-0295</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 부산진구 중앙대로666번길 50 201동 지하2층 5-13호</t>
+          <t>부산 부산진구 서전로37번길 18 지하1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mutgym_seomyeon_2</t>
+          <t>http://www.instagram.com/otaku_gym</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wm5u9og</t>
+          <t>https://talk.naver.com/ct/w46zlb</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>544</v>
+        <v>176</v>
       </c>
       <c r="Q7" t="n">
-        <v>419</v>
+        <v>112</v>
       </c>
       <c r="R7" t="n">
-        <v>963</v>
+        <v>288</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1130,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2036420985</t>
+          <t>37883160</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2036420985</t>
+          <t>https://m.place.naver.com/place/37883160</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1152,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>서면PT &amp; 헬스 놈짐 전포본점</t>
+          <t>헬짐 HELL GYM</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nomgym@naver.com</t>
+          <t>hellgymseomyeon@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1448-6113</t>
+          <t>0507-1435-7378</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 62 2F 서면PT &amp; 헬스 놈짐 전포본점</t>
+          <t>부산 부산진구 전포대로199번길 15 현대오피스텔 지하1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nom_gym</t>
+          <t>https://blog.naver.com/hellgymseomyeon</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1189,19 +1189,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w423c4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1213,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1378</v>
+        <v>729</v>
       </c>
       <c r="Q8" t="n">
-        <v>820</v>
+        <v>493</v>
       </c>
       <c r="R8" t="n">
-        <v>2198</v>
+        <v>1222</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,51 +1224,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1845202882</t>
+          <t>1847755059</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845202882</t>
+          <t>https://m.place.naver.com/place/1847755059</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>아르케 핏 PT 서면전포점</t>
+          <t>코코아짐 헬스 PT 스쿼시 범내골역점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>zon_t@naver.com</t>
+          <t>cocoagymbn@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1345-6738</t>
+          <t>0507-1374-1945</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 부산진구 전포대로209번길 43 아세아빌딩 지하1층</t>
+          <t>부산 부산진구 범일로 181 지하1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/arkhe_fit</t>
+          <t>https://blog.naver.com/cocoagymbn</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1287,7 +1283,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1297,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w42pxo</t>
+          <t>https://talk.naver.com/ct/whhuq4g</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>157</v>
+        <v>53</v>
       </c>
       <c r="Q9" t="n">
-        <v>323</v>
+        <v>103</v>
       </c>
       <c r="R9" t="n">
-        <v>480</v>
+        <v>156</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,51 +1322,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1578556277</t>
+          <t>2057373274</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1578556277</t>
+          <t>https://m.place.naver.com/place/2057373274</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>우노짐 헬스&amp;PT 서면점</t>
+          <t>아르케 핏 PT 서면전포점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>unogym_1@naver.com</t>
+          <t>zon_t@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1426-0888</t>
+          <t>0507-1345-6738</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산 부산진구 부전로 94 영동프라자 3층</t>
+          <t>부산 부산진구 전포대로209번길 43 아세아빌딩 지하1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/unogym_1</t>
+          <t>https://www.instagram.com/arkhe_fit</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1385,7 +1381,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1395,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w0m3yqq</t>
+          <t>https://talk.naver.com/ct/w42pxo</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1409,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>84</v>
+        <v>157</v>
       </c>
       <c r="Q10" t="n">
-        <v>31</v>
+        <v>323</v>
       </c>
       <c r="R10" t="n">
-        <v>115</v>
+        <v>480</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,115 +1420,213 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026422991</t>
+          <t>1578556277</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2026422991</t>
+          <t>https://m.place.naver.com/place/1578556277</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>뉴짐스</t>
+          <t>우노짐 헬스&amp;PT 서면점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>newgyms@naver.com</t>
+          <t>unogym_1@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1313-2236</t>
+          <t>0507-1426-0888</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>부산 부산진구 부전로 94 영동프라자 3층</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/unogym_1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w0m3yqq</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>31</v>
+      </c>
+      <c r="R11" t="n">
+        <v>115</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2026422991</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2026422991</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>뉴짐스</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>newgyms@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1313-2236</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>부산 부산진구 서전로38번길 66 3층</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>https://www.instagram.com/n.gyms_official</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/w438s8</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
         <v>66</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q12" t="n">
         <v>60</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>126</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>1810951830</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1810951830</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/서면_PT.xlsx
+++ b/naver-place-crawler/results_health/서면_PT.xlsx
@@ -422,12 +422,12 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -657,34 +657,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
+          <t>글래드휘트니스 서면점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fmpt__teddy@naver.com</t>
+          <t>gladfitness_seomyeon@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1343-6817</t>
+          <t>051-802-9900</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
+          <t>부산 부산진구 동천로 4 지오플레이스 6층 6002호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sksoe31e</t>
+          <t>https://blog.naver.com/gladfitness_seomyeon/223250547892</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4fpwi</t>
+          <t>https://talk.naver.com/ct/w4eq2q</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1092</v>
+        <v>632</v>
       </c>
       <c r="Q3" t="n">
-        <v>849</v>
+        <v>490</v>
       </c>
       <c r="R3" t="n">
-        <v>1941</v>
+        <v>1122</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1138689357</t>
+          <t>1673829593</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138689357</t>
+          <t>https://m.place.naver.com/place/1673829593</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>마카라멀티짐 서면점</t>
+          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>jhs850720@naver.com</t>
+          <t>fmpt__teddy@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1319-8423</t>
+          <t>0507-1343-6817</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산 부산진구 서면로 56 서면시장 3층</t>
+          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jhs850720</t>
+          <t>https://open.kakao.com/o/sksoe31e</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4dqw0</t>
+          <t>https://talk.naver.com/ct/w4fpwi</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>275</v>
+        <v>1092</v>
       </c>
       <c r="Q4" t="n">
-        <v>901</v>
+        <v>849</v>
       </c>
       <c r="R4" t="n">
-        <v>1176</v>
+        <v>1941</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>33964145</t>
+          <t>1138689357</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33964145</t>
+          <t>https://m.place.naver.com/place/1138689357</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>멋짐 서면2호점</t>
+          <t>마카라멀티짐 서면점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mutgym_@naver.com</t>
+          <t>jhs850720@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1378-8691</t>
+          <t>0507-1319-8423</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산 부산진구 중앙대로666번길 50 201동 지하2층 5-13호</t>
+          <t>부산 부산진구 서면로 56 서면시장 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mutgym_seomyeon_2</t>
+          <t>https://blog.naver.com/jhs850720</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wm5u9og</t>
+          <t>https://talk.naver.com/ct/w4dqw0</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>544</v>
+        <v>275</v>
       </c>
       <c r="Q5" t="n">
-        <v>419</v>
+        <v>901</v>
       </c>
       <c r="R5" t="n">
-        <v>963</v>
+        <v>1176</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2036420985</t>
+          <t>33964145</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2036420985</t>
+          <t>https://m.place.naver.com/place/33964145</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -956,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>서면PT &amp; 헬스 놈짐 전포본점</t>
+          <t>멋짐 서면2호점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nomgym@naver.com</t>
+          <t>mutgym_@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1448-6113</t>
+          <t>0507-1378-8691</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 62 2F 서면PT &amp; 헬스 놈짐 전포본점</t>
+          <t>부산 부산진구 중앙대로666번길 50 201동 지하2층 5-13호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nom_gym</t>
+          <t>https://www.instagram.com/mutgym_seomyeon_2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w423c4</t>
+          <t>https://talk.naver.com/ct/wm5u9og</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1378</v>
+        <v>544</v>
       </c>
       <c r="Q6" t="n">
-        <v>820</v>
+        <v>419</v>
       </c>
       <c r="R6" t="n">
-        <v>2198</v>
+        <v>963</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1845202882</t>
+          <t>2036420985</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845202882</t>
+          <t>https://m.place.naver.com/place/2036420985</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1054,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>오타쿠짐 서면점</t>
+          <t>서면PT &amp; 헬스 놈짐 전포본점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>taehu12@naver.com</t>
+          <t>nomgym@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1417-0295</t>
+          <t>0507-1448-6113</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 부산진구 서전로37번길 18 지하1층</t>
+          <t>부산 부산진구 동천로 62 2F 서면PT &amp; 헬스 놈짐 전포본점</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/otaku_gym</t>
+          <t>https://www.instagram.com/nom_gym</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w46zlb</t>
+          <t>https://talk.naver.com/ct/w423c4</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>176</v>
+        <v>1378</v>
       </c>
       <c r="Q7" t="n">
-        <v>112</v>
+        <v>820</v>
       </c>
       <c r="R7" t="n">
-        <v>288</v>
+        <v>2198</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>37883160</t>
+          <t>1845202882</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37883160</t>
+          <t>https://m.place.naver.com/place/1845202882</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1152,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>헬짐 HELL GYM</t>
+          <t>오타쿠짐 서면점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>hellgymseomyeon@naver.com</t>
+          <t>taehu12@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1435-7378</t>
+          <t>0507-1417-0295</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산 부산진구 전포대로199번길 15 현대오피스텔 지하1층</t>
+          <t>부산 부산진구 서전로37번길 18 지하1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hellgymseomyeon</t>
+          <t>http://www.instagram.com/otaku_gym</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1189,15 +1189,19 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46zlb</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1209,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>729</v>
+        <v>176</v>
       </c>
       <c r="Q8" t="n">
-        <v>493</v>
+        <v>112</v>
       </c>
       <c r="R8" t="n">
-        <v>1222</v>
+        <v>288</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1847755059</t>
+          <t>37883160</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1847755059</t>
+          <t>https://m.place.naver.com/place/37883160</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1241,34 +1245,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>코코아짐 헬스 PT 스쿼시 범내골역점</t>
+          <t>헬짐 HELL GYM</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cocoagymbn@naver.com</t>
+          <t>hellgymseomyeon@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1374-1945</t>
+          <t>0507-1435-7378</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 부산진구 범일로 181 지하1층</t>
+          <t>부산 부산진구 전포대로199번길 15 현대오피스텔 지하1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cocoagymbn</t>
+          <t>https://blog.naver.com/hellgymseomyeon</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1288,14 +1292,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/whhuq4g</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>53</v>
+        <v>729</v>
       </c>
       <c r="Q9" t="n">
-        <v>103</v>
+        <v>493</v>
       </c>
       <c r="R9" t="n">
-        <v>156</v>
+        <v>1222</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2057373274</t>
+          <t>1847755059</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2057373274</t>
+          <t>https://m.place.naver.com/place/1847755059</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1339,34 +1339,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>아르케 핏 PT 서면전포점</t>
+          <t>코코아짐 헬스 PT 스쿼시 범내골역점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>zon_t@naver.com</t>
+          <t>cocoagymbn@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1345-6738</t>
+          <t>0507-1374-1945</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산 부산진구 전포대로209번길 43 아세아빌딩 지하1층</t>
+          <t>부산 부산진구 범일로 181 지하1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/arkhe_fit</t>
+          <t>https://blog.naver.com/cocoagymbn</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w42pxo</t>
+          <t>https://talk.naver.com/ct/whhuq4g</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>157</v>
+        <v>53</v>
       </c>
       <c r="Q10" t="n">
-        <v>323</v>
+        <v>103</v>
       </c>
       <c r="R10" t="n">
-        <v>480</v>
+        <v>156</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1578556277</t>
+          <t>2057373274</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1578556277</t>
+          <t>https://m.place.naver.com/place/2057373274</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1437,34 +1437,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>우노짐 헬스&amp;PT 서면점</t>
+          <t>아르케 핏 PT 서면전포점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>unogym_1@naver.com</t>
+          <t>zon_t@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1426-0888</t>
+          <t>0507-1345-6738</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산 부산진구 부전로 94 영동프라자 3층</t>
+          <t>부산 부산진구 전포대로209번길 43 아세아빌딩 지하1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/unogym_1</t>
+          <t>https://www.instagram.com/arkhe_fit</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w0m3yqq</t>
+          <t>https://talk.naver.com/ct/w42pxo</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>84</v>
+        <v>157</v>
       </c>
       <c r="Q11" t="n">
-        <v>31</v>
+        <v>323</v>
       </c>
       <c r="R11" t="n">
-        <v>115</v>
+        <v>480</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026422991</t>
+          <t>1578556277</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2026422991</t>
+          <t>https://m.place.naver.com/place/1578556277</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1535,34 +1535,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>뉴짐스</t>
+          <t>우노짐 헬스&amp;PT 서면점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>newgyms@naver.com</t>
+          <t>unogym_1@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1313-2236</t>
+          <t>0507-1426-0888</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>부산 부산진구 서전로38번길 66 3층</t>
+          <t>부산 부산진구 부전로 94 영동프라자 3층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/n.gyms_official</t>
+          <t>https://blog.naver.com/unogym_1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w438s8</t>
+          <t>https://talk.naver.com/ct/w0m3yqq</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1601,13 +1601,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="Q12" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="R12" t="n">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1616,12 +1616,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1810951830</t>
+          <t>2026422991</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1810951830</t>
+          <t>https://m.place.naver.com/place/2026422991</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
